--- a/Result/profitability/3224.xlsx
+++ b/Result/profitability/3224.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.27125</v>
+        <v>-0.2625</v>
       </c>
       <c r="N2" t="n">
-        <v>12.79875</v>
+        <v>12.83125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-1.02</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.37625</v>
+        <v>-0.35</v>
       </c>
       <c r="N3" t="n">
-        <v>11.79625</v>
+        <v>12.0025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3474999999999999</v>
+        <v>-0.3362499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11.14</v>
+        <v>11.3375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.09</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.45875</v>
+        <v>-0.395</v>
       </c>
       <c r="N5" t="n">
-        <v>10.45</v>
+        <v>10.53</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.405</v>
+        <v>-0.38875</v>
       </c>
       <c r="N6" t="n">
-        <v>10.0675</v>
+        <v>10.2425</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.93</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.49125</v>
+        <v>-0.445</v>
       </c>
       <c r="N7" t="n">
-        <v>9.788749999999999</v>
+        <v>9.59625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.39875</v>
+        <v>-0.41625</v>
       </c>
       <c r="N8" t="n">
-        <v>9.285</v>
+        <v>8.9625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02375000000000006</v>
+        <v>0.02375000000000003</v>
       </c>
       <c r="N13" t="n">
         <v>10.52625</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>417</v>
+      </c>
+      <c r="D75" t="n">
+        <v>360</v>
+      </c>
+      <c r="E75" t="n">
+        <v>57</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-11.65%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-46</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.265</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.39375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.579999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1597523219814241</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8225806451612903</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.6400000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04949729311678275</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
